--- a/data/Isotopes/output/isotope_intersections.xlsx
+++ b/data/Isotopes/output/isotope_intersections.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/Isotopes/output/isotope_intersections.xlsx
+++ b/data/Isotopes/output/isotope_intersections.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U86"/>
+  <dimension ref="A1:U84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,7 +533,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -543,48 +543,84 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="R2" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>CU269</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -604,22 +640,14 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -643,28 +671,20 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>CU431</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
@@ -672,37 +692,41 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>CU477</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -717,17 +741,9 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -753,7 +769,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>CU478</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -763,7 +779,11 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -773,7 +793,11 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -808,50 +832,62 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>EXMFT003</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
       <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>EXMFT013</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -861,11 +897,7 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -875,22 +907,14 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -914,24 +938,20 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>EXMFT033</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
@@ -939,100 +959,168 @@
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
+          <t>EXMFT050</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr"/>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr"/>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>EXMFT060</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
@@ -1040,14 +1128,26 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -1071,138 +1171,74 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
+          <t>EXMFT070</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>✖️</t>
+          <t>✔️</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
         <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+          <t>EXMFT071</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
@@ -1210,26 +1246,14 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -1253,7 +1277,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>EXMFT096</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -1308,7 +1332,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>EXMFT109</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -1328,14 +1352,22 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -1359,7 +1391,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>EXMFT112</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -1369,7 +1401,11 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -1379,7 +1415,11 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -1414,19 +1454,31 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t>EXMFT134</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
@@ -1444,7 +1496,11 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -1468,12 +1524,16 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>ICT005</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1483,11 +1543,7 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -1497,11 +1553,7 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -1536,76 +1588,56 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+          <t>ICT006</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -1615,19 +1647,31 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>ISic000004</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
@@ -1635,13 +1679,21 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -1670,56 +1722,52 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>ISic000027</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="U21" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -1729,31 +1777,19 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+          <t>ISic000028</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
@@ -1761,26 +1797,14 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -1804,7 +1828,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>ISic000034</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1819,11 +1843,7 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
@@ -1850,16 +1870,12 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>ISic000036</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1910,7 +1926,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>ISic000068</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1920,20 +1936,40 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -1952,12 +1988,16 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>ISic000069</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1969,7 +2009,11 @@
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
@@ -1977,14 +2021,22 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -2003,60 +2055,36 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>ISic000097</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -2079,10 +2107,14 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
+          <t>ISic000104</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
@@ -2091,11 +2123,7 @@
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
@@ -2137,36 +2165,64 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>ISic000121</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -2189,14 +2245,10 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+          <t>ISic000148</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
@@ -2213,11 +2265,7 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -2252,43 +2300,31 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
+          <t>ISic000163</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -2313,21 +2349,13 @@
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>ISic000178</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -2382,7 +2410,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>ISic000181</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2391,28 +2419,44 @@
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -2424,7 +2468,11 @@
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="R33" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -2432,12 +2480,16 @@
       </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>ISic000184</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -2492,14 +2544,10 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+          <t>ISic000207</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
@@ -2508,11 +2556,7 @@
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -2524,43 +2568,27 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
@@ -2571,43 +2599,27 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>ISic000220</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
@@ -2621,12 +2633,16 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>ISic000227</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -2652,11 +2668,7 @@
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
@@ -2666,11 +2678,7 @@
         </is>
       </c>
       <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
@@ -2681,13 +2689,17 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>ISic000229</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
@@ -2696,25 +2708,25 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -2724,19 +2736,19 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>ISic000232</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -2748,20 +2760,32 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="U39" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -2771,24 +2795,20 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>ISic000281</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
@@ -2796,88 +2816,144 @@
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+          <t>ISic000366</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>✔️</t>
+          <t>✖️</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>✔️</t>
+          <t>✖️</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr"/>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>✔️</t>
+          <t>✖️</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>✔️</t>
+          <t>✖️</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>ISic000368</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2928,114 +3004,58 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
+          <t>ISic000579</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr">
         <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>ISic000711</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -3086,20 +3106,20 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>ISic000725</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
@@ -3107,18 +3127,14 @@
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr">
@@ -3132,24 +3148,40 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
+          <t>ISic000729</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
@@ -3157,14 +3189,26 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -3178,17 +3222,13 @@
         </is>
       </c>
       <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>ISic000871</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -3196,7 +3236,11 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -3208,7 +3252,11 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
@@ -3216,7 +3264,11 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr">
@@ -3239,31 +3291,19 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+          <t>ISic001120</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
@@ -3271,21 +3311,13 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -3304,19 +3336,31 @@
         </is>
       </c>
       <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
+          <t>ISic001135</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
@@ -3334,36 +3378,32 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="R49" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
       <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -3373,20 +3413,20 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>ISic001158</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
@@ -3394,50 +3434,42 @@
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+          <t>ISic001399</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -3449,43 +3481,47 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
       <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="U51" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -3495,54 +3531,114 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+          <t>ISic001435</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>✔️</t>
+          <t>✖️</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>ISic003300</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -3552,17 +3648,9 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
@@ -3570,11 +3658,7 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -3613,114 +3697,74 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>ISic003335</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>✖️</t>
+          <t>✔️</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>✖️</t>
+          <t>✔️</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>✖️</t>
+          <t>✔️</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>✖️</t>
+          <t>✔️</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>✖️</t>
+          <t>✔️</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>✖️</t>
+          <t>✔️</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr">
         <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>ISic004341</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -3747,11 +3791,7 @@
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -3770,34 +3810,22 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+          <t>ISic004363</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
@@ -3807,21 +3835,13 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -3840,13 +3860,17 @@
         </is>
       </c>
       <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="U56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>ISic004364</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -3856,24 +3880,44 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="O57" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -3892,12 +3936,16 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>ISic004365</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -3924,11 +3972,7 @@
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -3952,7 +3996,7 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>MARPO102146</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -3962,44 +4006,24 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -4018,67 +4042,47 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>MARPO102147</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>MARPO107187</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -4129,25 +4133,45 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
+          <t>MARPO14450</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -4155,16 +4179,28 @@
       </c>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>MARPO15577</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -4174,24 +4210,40 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="O63" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -4210,12 +4262,16 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr"/>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>MARPO15585</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4224,7 +4280,11 @@
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -4247,8 +4307,16 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -4259,7 +4327,11 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr"/>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
         <is>
@@ -4282,16 +4354,16 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
+          <t>MARPO176+162</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -4314,13 +4386,17 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -4332,18 +4408,18 @@
         </is>
       </c>
       <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="R65" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
       <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -4353,97 +4429,61 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+          <t>MARPO252</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
       <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
       <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+          <t>MARPO253</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
@@ -4469,38 +4509,26 @@
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr">
         <is>
@@ -4511,7 +4539,7 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>MARPO254</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -4526,17 +4554,9 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
@@ -4562,56 +4582,64 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>MARPO33266</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="T69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="U69" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -4621,7 +4649,7 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>MARPO5</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -4636,11 +4664,27 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="O70" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -4664,74 +4708,70 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
+          <t>ORSI099</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>ORSI136</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -4751,22 +4791,14 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -4790,14 +4822,10 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+          <t>ORSI291</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
@@ -4805,11 +4833,7 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -4845,15 +4869,23 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr"/>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
-      <c r="U73" t="inlineStr"/>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>ORSI316</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -4863,7 +4895,11 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
@@ -4873,14 +4909,22 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="O74" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -4904,201 +4948,193 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>ORSI329</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
       <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
+          <t>ORSI330</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="R76" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
       <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>ORSI340</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="R77" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
       <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+          <t>ORSI373</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
@@ -5106,62 +5142,50 @@
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
       <c r="S78" t="inlineStr"/>
-      <c r="T78" t="inlineStr"/>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>ORSI416</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
@@ -5169,54 +5193,62 @@
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
       <c r="S79" t="inlineStr"/>
-      <c r="T79" t="inlineStr"/>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>ORSI431</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
@@ -5224,37 +5256,37 @@
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>ORSI436</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -5274,14 +5306,22 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="O81" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -5305,7 +5345,7 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>ORSI437</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -5316,16 +5356,8 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -5339,12 +5371,12 @@
       </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr">
@@ -5352,12 +5384,12 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr">
         <is>
@@ -5368,7 +5400,7 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>SALINAS5644</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -5388,22 +5420,14 @@
           <t>✔️</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr">
         <is>
           <t>✔️</t>
@@ -5427,24 +5451,20 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>SALINASTINDARI</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
@@ -5452,134 +5472,32 @@
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
+      <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr">
         <is>
           <t>✔️</t>
         </is>
       </c>
       <c r="S84" t="inlineStr"/>
-      <c r="T84" t="inlineStr"/>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="1" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="S85" t="inlineStr"/>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="1" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="S86" t="inlineStr"/>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>✔️</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr"/>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>✔️</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
